--- a/ReporteGasolina/Evidencias/Precio Gasolina por Zona 08-2026.xlsx
+++ b/ReporteGasolina/Evidencias/Precio Gasolina por Zona 08-2026.xlsx
@@ -370,11 +370,11 @@
       <x:protection locked="1" hidden="0"/>
     </x:xf>
     <x:xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <x:alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
     <x:xf numFmtId="164" fontId="1" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <x:alignment horizontal="right" vertical="bottom" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <x:alignment horizontal="right" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
@@ -390,6 +390,42 @@
     <x:cellStyle name="Normal" xfId="0" builtinId="0"/>
   </x:cellStyles>
 </x:styleSheet>
+</file>
+
+<file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
+  <xdr:oneCellAnchor>
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>0</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:ext cx="2152650" cy="809625"/>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="1" name="Logo"/>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip r:embed="rId6" cstate="print"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="0"/>
+          <a:ext cx="2152650" cy="809625"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect"/>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:oneCellAnchor>
+</xdr:wsDr>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -704,7 +740,7 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="F2" s="3">
-        <x:v>46240.5902284144</x:v>
+        <x:v>46241.6859302315</x:v>
       </x:c>
     </x:row>
     <x:row r="3" spans="1:6">
@@ -1407,6 +1443,7 @@
   <x:pageMargins left="0.75" right="0.75" top="0.75" bottom="0.5" header="0.5" footer="0.75"/>
   <x:pageSetup paperSize="1" scale="100" pageOrder="downThenOver" orientation="default" blackAndWhite="0" draft="0" cellComments="none" errors="displayed"/>
   <x:headerFooter/>
+  <x:drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId5"/>
   <x:tableParts count="0"/>
 </x:worksheet>
 </file>